--- a/교재/엑셀교재v2/026_시나리오_실습.xlsx
+++ b/교재/엑셀교재v2/026_시나리오_실습.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompUse2nd\교재\엑셀교재v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FORYOUCOM\Documents\CompUse2nd\교재\엑셀교재v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54064B56-ADDE-4A23-B3EE-37296FED9B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2E15C1-84CD-412B-A21E-7C071D50E874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="사용안내" sheetId="1" r:id="rId1"/>
@@ -20,26 +20,13 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">사용안내!$A$1:$D$18</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">시나리오!$A$1:$G$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">시나리오!$A$1:$G$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'시나리오 요약보고서'!$B$2:$F$11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">시나리오_실습!$A$1:$G$23</definedName>
     <definedName name="불량률">시나리오!$G$14</definedName>
     <definedName name="손실금액합계">시나리오!$G$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -151,24 +138,9 @@
     <t>불량률</t>
   </si>
   <si>
-    <t>문제: 불량률증가 7%, 불량률감소 3%를 저장하고 손실금액합계의 요약 보고서를 만드세요.</t>
-  </si>
-  <si>
-    <t>G14 이름 불량률 / G12 이름 손실금액합계. 변경 셀 G14 / 결과 셀 G12.</t>
-  </si>
-  <si>
     <t>메뉴: 데이터 → 가상 분석 → 시나리오 관리자 → 추가 → 요약.</t>
   </si>
   <si>
-    <t>자료: 촬영 노트 026페이지. 원본 판매표가 없어 합계 33,730,000인 학습 자료로 구성했습니다.</t>
-  </si>
-  <si>
-    <t>사진의 결과와 일치: 5% 1,686,500 / 7% 2,361,100 / 3% 1,011,900.</t>
-  </si>
-  <si>
-    <t>불량수량은 비율로 추정한 수량이며 소수가 나올 수 있습니다. 손실금액은 판매금액 × 불량률입니다.</t>
-  </si>
-  <si>
     <t>손실금액합계</t>
   </si>
   <si>
@@ -203,13 +175,28 @@
   </si>
   <si>
     <t>회색으로 표시됩니다.</t>
+  </si>
+  <si>
+    <t>판매현황’표에서 불량률[G14]이 변동하는 경우 손실금액 합계[G12]의 변동 시나리오를 작성하시오.</t>
+  </si>
+  <si>
+    <t>▶ 셀 이름 정의 : [G14] 셀은 ‘불량률’, [G12] 셀은 ‘손실금액합계’로 정의하시오.</t>
+  </si>
+  <si>
+    <t>▶ 시나리오1 : 시나리오 이름은 ‘불량률증가’, 수익률은 ‘7%’로 설정하시오.</t>
+  </si>
+  <si>
+    <t>▶ 시나리오2 : 시나리오 이름은 ‘불량률감소’, 수익률은 ‘3%’로 설정하시오.</t>
+  </si>
+  <si>
+    <t>▶ ‘시나리오 요약’보고서는 ‘분석작업’ 시트 바로 앞에 위치시키시오.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -263,6 +250,12 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -352,7 +345,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -379,49 +372,52 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -646,12 +642,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="36" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="1:4" ht="36" customHeight="1">
       <c r="A2" s="1"/>
@@ -660,132 +656,132 @@
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="36" customHeight="1">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
     </row>
     <row r="4" spans="1:4" ht="36" customHeight="1">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
     </row>
     <row r="5" spans="1:4" ht="36" customHeight="1">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
     </row>
     <row r="6" spans="1:4" ht="36" customHeight="1">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
     </row>
     <row r="7" spans="1:4" ht="36" customHeight="1">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
     </row>
     <row r="8" spans="1:4" ht="36" customHeight="1">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
     </row>
     <row r="9" spans="1:4" ht="36" customHeight="1">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
     </row>
     <row r="10" spans="1:4" ht="36" customHeight="1">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
     </row>
     <row r="11" spans="1:4" ht="36" customHeight="1">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
     </row>
     <row r="12" spans="1:4" ht="36" customHeight="1">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
     </row>
     <row r="13" spans="1:4" ht="36" customHeight="1">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
     </row>
     <row r="14" spans="1:4" ht="36" customHeight="1">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
     </row>
     <row r="15" spans="1:4" ht="36" customHeight="1">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
     </row>
     <row r="16" spans="1:4" ht="36" customHeight="1">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
     </row>
     <row r="17" spans="1:4" ht="36" customHeight="1">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
     </row>
     <row r="18" spans="1:4" ht="36" customHeight="1">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
     </row>
     <row r="19" spans="1:4" ht="36" customHeight="1">
       <c r="A19" s="1"/>
@@ -844,14 +840,14 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
@@ -1170,123 +1166,120 @@
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1">
       <c r="A16" s="2"/>
-      <c r="B16" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
+      <c r="B16" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1">
       <c r="A17" s="2"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="B17" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" ht="30" customHeight="1">
       <c r="A18" s="2"/>
-      <c r="B18" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
+      <c r="B18" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" ht="30" customHeight="1">
       <c r="A19" s="2"/>
-      <c r="B19" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
+      <c r="B19" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" ht="30" customHeight="1">
       <c r="A20" s="2"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="B20" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9" ht="36" customHeight="1">
       <c r="A21" s="2"/>
-      <c r="B21" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9" ht="36" customHeight="1">
       <c r="A22" s="2"/>
-      <c r="B22" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9" ht="36" customHeight="1">
       <c r="A23" s="2"/>
-      <c r="B23" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
     </row>
     <row r="24" spans="1:9" ht="30" customHeight="1">
       <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
+      <c r="B24" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B22:G22"/>
+  <mergeCells count="4">
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="B23:G23"/>
     <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:G19"/>
     <mergeCell ref="B21:G21"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -1310,119 +1303,119 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.25" thickBot="1">
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="2" spans="2:6" ht="16.5">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+    </row>
+    <row r="3" spans="2:6" ht="16.5" collapsed="1">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="16.5" hidden="1" outlineLevel="1">
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="16.5">
+      <c r="B5" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+    </row>
+    <row r="6" spans="2:6" ht="16.5" outlineLevel="1">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="18">
+        <v>0.05</v>
+      </c>
+      <c r="E6" s="19">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F6" s="19">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="16.5">
+      <c r="B7" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="2:6" ht="17.25" outlineLevel="1" thickBot="1">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="21">
+        <v>1686500</v>
+      </c>
+      <c r="E8" s="21">
+        <v>2361100</v>
+      </c>
+      <c r="F8" s="21">
+        <v>1011900</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="16.5">
+      <c r="B9" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" spans="2:6" ht="16.5">
+      <c r="B10" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-    </row>
-    <row r="3" spans="2:6" ht="16.5" collapsed="1">
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="33" hidden="1" outlineLevel="1">
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" ht="16.5">
-      <c r="B5" s="23" t="s">
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="2:6" ht="16.5">
+      <c r="B11" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-    </row>
-    <row r="6" spans="2:6" ht="16.5" outlineLevel="1">
-      <c r="B6" s="21"/>
-      <c r="C6" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="25">
-        <v>0.05</v>
-      </c>
-      <c r="E6" s="26">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F6" s="26">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" ht="16.5">
-      <c r="B7" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-    </row>
-    <row r="8" spans="2:6" ht="17.25" outlineLevel="1" thickBot="1">
-      <c r="B8" s="27"/>
-      <c r="C8" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="28">
-        <v>1686500</v>
-      </c>
-      <c r="E8" s="28">
-        <v>2361100</v>
-      </c>
-      <c r="F8" s="28">
-        <v>1011900</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" ht="16.5">
-      <c r="B9" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-    </row>
-    <row r="10" spans="2:6" ht="16.5">
-      <c r="B10" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-    </row>
-    <row r="11" spans="2:6" ht="16.5">
-      <c r="B11" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -1436,7 +1429,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -1450,14 +1443,14 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1">
       <c r="A1" s="2"/>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
@@ -1776,114 +1769,180 @@
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1">
       <c r="A16" s="2"/>
-      <c r="B16" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1">
       <c r="A17" s="2"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="B17" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" ht="30" customHeight="1">
       <c r="A18" s="2"/>
-      <c r="B18" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
+      <c r="B18" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" ht="30" customHeight="1">
       <c r="A19" s="2"/>
-      <c r="B19" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
+      <c r="B19" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" ht="30" customHeight="1">
       <c r="A20" s="2"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="B20" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
-    <row r="21" spans="1:9" ht="36" customHeight="1">
+    <row r="21" spans="1:9" ht="30" customHeight="1">
       <c r="A21" s="2"/>
-      <c r="B21" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
+      <c r="B21" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
     </row>
-    <row r="22" spans="1:9" ht="36" customHeight="1">
+    <row r="22" spans="1:9" ht="30" customHeight="1">
       <c r="A22" s="2"/>
-      <c r="B22" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
     </row>
-    <row r="23" spans="1:9" ht="36" customHeight="1">
+    <row r="23" spans="1:9" ht="30" customHeight="1">
       <c r="A23" s="2"/>
-      <c r="B23" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
     </row>
     <row r="24" spans="1:9" ht="30" customHeight="1">
       <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" ht="30" customHeight="1">
+      <c r="A25" s="2"/>
+      <c r="B25" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" ht="30" customHeight="1">
+      <c r="A26" s="2"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" ht="36" customHeight="1">
+      <c r="A27" s="2"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:9" ht="36" customHeight="1">
+      <c r="A28" s="2"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" spans="1:9" ht="36" customHeight="1">
+      <c r="A29" s="2"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="1:9" ht="30" customHeight="1">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
     </row>
   </sheetData>
   <scenarios current="0" show="0" sqref="G12">
@@ -1895,13 +1954,13 @@
     </scenario>
   </scenarios>
   <mergeCells count="7">
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B1:G1"/>
     <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B27:G27"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
